--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484153_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484153_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1027</v>
+        <v>2.1104</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0754</v>
+        <v>2.0551</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0273</v>
+        <v>0.0554</v>
       </c>
       <c r="G2" t="n">
         <v>0.3122</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>1.005</v>
+        <v>0.0128</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9807</v>
+        <v>-0.0396</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0243</v>
+        <v>0.0524</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5255</v>
+        <v>2.0715</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9114</v>
+        <v>1.4012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6141</v>
+        <v>0.6702</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2177</v>
@@ -688,13 +688,13 @@
         <v>3.1741</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5646</v>
+        <v>0.1106</v>
       </c>
       <c r="T3" t="n">
-        <v>0.618</v>
+        <v>0.1078</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0534</v>
+        <v>0.0027</v>
       </c>
       <c r="V3" t="n">
         <v>0.1947</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5926</v>
+        <v>-0.3262</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5425</v>
+        <v>-1.2761</v>
       </c>
       <c r="F4" t="n">
         <v>0.9499</v>
@@ -766,10 +766,10 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1643</v>
+        <v>0.1021</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1076</v>
+        <v>0.1588</v>
       </c>
       <c r="U4" t="n">
         <v>-0.0567</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8085</v>
+        <v>-1.5803</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.1814</v>
+        <v>-2.813</v>
       </c>
       <c r="F5" t="n">
-        <v>1.373</v>
+        <v>1.2327</v>
       </c>
       <c r="G5" t="n">
         <v>-2.7409</v>
@@ -844,13 +844,13 @@
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3373</v>
+        <v>0.5655</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2323</v>
+        <v>0.1361</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5696</v>
+        <v>0.4293</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0481</v>
+        <v>-2.098</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1694</v>
+        <v>-0.107</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8788</v>
+        <v>-1.991</v>
       </c>
       <c r="G6" t="n">
         <v>-3.0455</v>
@@ -922,13 +922,13 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4183</v>
+        <v>0.3685</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0057</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4126</v>
+        <v>0.3004</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2065</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1018</v>
+        <v>-2.7828</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7645</v>
+        <v>-2.9686</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6627</v>
+        <v>0.1858</v>
       </c>
       <c r="G7" t="n">
         <v>-3.7502</v>
@@ -1000,13 +1000,13 @@
         <v>2.3806</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1841</v>
+        <v>0.5031</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1135</v>
+        <v>-0.0906</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0706</v>
+        <v>0.5936</v>
       </c>
       <c r="V7" t="n">
         <v>0.266</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5533</v>
+        <v>-3.4609</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8232</v>
+        <v>-3.3934</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7301</v>
+        <v>-0.0674</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5875</v>
+        <v>-6.8723</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3627</v>
+        <v>-0.4281</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.9502</v>
+        <v>-6.4442</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3188</v>
+        <v>-3.415</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7594</v>
+        <v>0.626</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0782</v>
+        <v>-4.041</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.2687</v>
+        <v>-3.4573</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3967</v>
+        <v>-1.0541</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.872</v>
+        <v>-2.4032</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3806</v>
+        <v>3.1741</v>
       </c>
       <c r="S8" t="n">
-        <v>0.118</v>
+        <v>-0.4534</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4876</v>
+        <v>-0.2606</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3696</v>
+        <v>-0.1928</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4724</v>
+        <v>1.881</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4724</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1036</v>
+        <v>-3.5267</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6995</v>
+        <v>-0.9649</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4041</v>
+        <v>-2.5618</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.8723</v>
+        <v>-3.5875</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4281</v>
+        <v>0.3627</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.4442</v>
+        <v>-3.9502</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.415</v>
+        <v>-0.3188</v>
       </c>
       <c r="K9" t="n">
-        <v>0.626</v>
+        <v>1.7594</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.041</v>
+        <v>-2.0782</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4573</v>
+        <v>-3.2687</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0541</v>
+        <v>-1.3967</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4032</v>
+        <v>-1.872</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1741</v>
+        <v>2.3806</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0962</v>
+        <v>0.1446</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5667</v>
+        <v>0.3458</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5294</v>
+        <v>-0.2013</v>
       </c>
       <c r="V9" t="n">
-        <v>1.881</v>
+        <v>-1.4724</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4085</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9161</v>
+        <v>-4.304</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.5875</v>
+        <v>-5.9753</v>
       </c>
       <c r="F10" t="n">
         <v>1.6714</v>
@@ -1234,10 +1234,10 @@
         <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7085</v>
+        <v>-0.0963</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0995</v>
+        <v>-0.4873</v>
       </c>
       <c r="U10" t="n">
         <v>0.391</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5215</v>
+        <v>-4.8088</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2083</v>
+        <v>-4.6358</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3133</v>
+        <v>-0.173</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6746</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5809</v>
+        <v>0.1318</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5384</v>
+        <v>0.0341</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0425</v>
+        <v>0.0978</v>
       </c>
       <c r="V11" t="n">
         <v>-0.266</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.0173</v>
+        <v>-18.7058</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.9895</v>
+        <v>-18.6778</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02790000000000104</v>
+        <v>-0.02780000000000021</v>
       </c>
       <c r="G12" t="n">
         <v>-27.6929</v>
@@ -1390,13 +1390,13 @@
         <v>20.8304</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0774</v>
+        <v>1.3893</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.339</v>
+        <v>-0.02740000000000006</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4165</v>
+        <v>1.4164</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3371999999999998</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0784</v>
+        <v>7.3972</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3977</v>
+        <v>5.2957</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6807</v>
+        <v>2.1016</v>
       </c>
       <c r="G13" t="n">
         <v>8.6967</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6263</v>
+        <v>-0.3075</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1303</v>
+        <v>-0.2323</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.496</v>
+        <v>-0.0752</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0971</v>
+        <v>5.5417</v>
       </c>
       <c r="E14" t="n">
         <v>4.3106</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7865</v>
+        <v>1.2311</v>
       </c>
       <c r="G14" t="n">
         <v>5.2205</v>
@@ -1546,13 +1546,13 @@
         <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3894</v>
+        <v>0.0552</v>
       </c>
       <c r="T14" t="n">
         <v>0.1191</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5085</v>
+        <v>-0.0639</v>
       </c>
       <c r="V14" t="n">
         <v>0.266</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5615</v>
+        <v>3.9282</v>
       </c>
       <c r="E15" t="n">
-        <v>0.278</v>
+        <v>0.074</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2835</v>
+        <v>3.8542</v>
       </c>
       <c r="G15" t="n">
         <v>5.2536</v>
@@ -1624,13 +1624,13 @@
         <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6885</v>
+        <v>0.0552</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1926</v>
+        <v>-0.3967</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8812</v>
+        <v>0.4519</v>
       </c>
       <c r="V15" t="n">
         <v>0.6032</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0965</v>
+        <v>3.4205</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7618</v>
+        <v>1.1699</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3347</v>
+        <v>2.2506</v>
       </c>
       <c r="G16" t="n">
         <v>2.9539</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3849</v>
+        <v>-0.061</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6858</v>
+        <v>-0.2777</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3009</v>
+        <v>0.2167</v>
       </c>
       <c r="V16" t="n">
         <v>-0.266</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8914</v>
+        <v>2.5275</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0609</v>
+        <v>-0.6731</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9523</v>
+        <v>3.2006</v>
       </c>
       <c r="G17" t="n">
         <v>4.9762</v>
@@ -1780,13 +1780,13 @@
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1768</v>
+        <v>-0.1871</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4876</v>
+        <v>-0.1246</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3108</v>
+        <v>-0.0625</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6745</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BARBECHO GARCIA</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.552</v>
+        <v>-0.1507</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4707</v>
+        <v>-3.8296</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0227</v>
+        <v>3.6789</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1702</v>
+        <v>0.8395</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.8273</v>
+        <v>2.0107</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6571</v>
+        <v>-1.1712</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.134</v>
+        <v>-0.9616</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2946</v>
+        <v>1.0388</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1606</v>
+        <v>-2.0004</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0363</v>
+        <v>1.801</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5327</v>
+        <v>0.9718</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4964</v>
+        <v>0.8292</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1984</v>
+        <v>-2.3806</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4606</v>
+        <v>0.2083</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8616</v>
+        <v>-0.4874</v>
       </c>
       <c r="U18" t="n">
-        <v>0.599</v>
+        <v>0.6956</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.532</v>
+        <v>-0.6032</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.532</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9048</v>
+        <v>-0.2206</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.3397</v>
+        <v>-2.5031</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4349</v>
+        <v>2.2825</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8395</v>
+        <v>1.4534</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0107</v>
+        <v>-0.9979</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1712</v>
+        <v>2.4513</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9616</v>
+        <v>0.4111</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0388</v>
+        <v>-0.2717</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0004</v>
+        <v>0.6827</v>
       </c>
       <c r="M19" t="n">
-        <v>1.801</v>
+        <v>1.0423</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9718</v>
+        <v>-0.7262</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8292</v>
+        <v>1.7685</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5952</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3806</v>
+        <v>-3.9677</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.1743</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.153</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4516</v>
+        <v>-0.0213</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6032</v>
+        <v>1.2777</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6032</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>P. BARBECHO GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1533</v>
+        <v>-0.2328</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9112</v>
+        <v>-1.0829</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7579</v>
+        <v>0.8501</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4534</v>
+        <v>-1.1702</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9979</v>
+        <v>-2.8273</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4513</v>
+        <v>1.6571</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4111</v>
+        <v>-1.134</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2717</v>
+        <v>-1.2946</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6827</v>
+        <v>0.1606</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0423</v>
+        <v>-0.0363</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7262</v>
+        <v>-1.5327</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7685</v>
+        <v>1.4964</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7774</v>
+        <v>0.7935</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9677</v>
+        <v>-0.1984</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.107</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5611</v>
+        <v>0.2495</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5459000000000001</v>
+        <v>0.4264</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2777</v>
+        <v>-0.532</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0713</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2014</v>
+        <v>-1.8332</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9376</v>
+        <v>-2.7336</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7363</v>
+        <v>0.9004</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5305</v>
@@ -2092,13 +2092,13 @@
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3498</v>
+        <v>0.0184</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3173</v>
+        <v>-0.1133</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0324</v>
+        <v>0.1317</v>
       </c>
       <c r="V21" t="n">
         <v>0.266</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>19.0174</v>
+        <v>20.3778</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02800000000000091</v>
+        <v>0.02790000000000159</v>
       </c>
       <c r="F22" t="n">
-        <v>18.9895</v>
+        <v>20.35</v>
       </c>
       <c r="G22" t="n">
         <v>27.6931</v>
@@ -2170,16 +2170,16 @@
         <v>12.8951</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0774</v>
+        <v>0.2830999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4163</v>
+        <v>-1.4164</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3390999999999999</v>
+        <v>1.6994</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3371999999999999</v>
+        <v>0.3372000000000002</v>
       </c>
       <c r="W22" t="n">
         <v>3.4056</v>
